--- a/documents/breakage_reports/TOOLS AND EQUIPMENT BREAKAGE MONITORING REPORT_May_2026.xlsx
+++ b/documents/breakage_reports/TOOLS AND EQUIPMENT BREAKAGE MONITORING REPORT_May_2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="22">
   <si>
     <t>TOOLS AND EQUIPMENT BREAKAGE MONITORING REPORT</t>
   </si>
@@ -44,6 +44,21 @@
     <t>nawala</t>
   </si>
   <si>
+    <t>Ashtray</t>
+  </si>
+  <si>
+    <t>nabasag</t>
+  </si>
+  <si>
+    <t>Blender</t>
+  </si>
+  <si>
+    <t>nasira ang isa</t>
+  </si>
+  <si>
+    <t>nasira</t>
+  </si>
+  <si>
     <t>Department Chair, BS</t>
   </si>
   <si>
@@ -62,10 +77,10 @@
     <t>Prepared by:</t>
   </si>
   <si>
-    <t>Ashtray</t>
-  </si>
-  <si>
-    <t>nabasag</t>
+    <t>Can opener</t>
+  </si>
+  <si>
+    <t>nawala ang isa</t>
   </si>
 </sst>
 </file>
@@ -418,7 +433,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
@@ -467,7 +482,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -476,31 +491,87 @@
         <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
         <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/documents/breakage_reports/TOOLS AND EQUIPMENT BREAKAGE MONITORING REPORT_May_2026.xlsx
+++ b/documents/breakage_reports/TOOLS AND EQUIPMENT BREAKAGE MONITORING REPORT_May_2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
   <si>
     <t>TOOLS AND EQUIPMENT BREAKAGE MONITORING REPORT</t>
   </si>
@@ -59,6 +59,12 @@
     <t>nasira</t>
   </si>
   <si>
+    <t>Can opener</t>
+  </si>
+  <si>
+    <t>nawala ang isa</t>
+  </si>
+  <si>
     <t>Department Chair, BS</t>
   </si>
   <si>
@@ -77,10 +83,10 @@
     <t>Prepared by:</t>
   </si>
   <si>
-    <t>Can opener</t>
-  </si>
-  <si>
-    <t>nawala ang isa</t>
+    <t>Bath towel</t>
+  </si>
+  <si>
+    <t>tinesting ko lang kanina mag add</t>
   </si>
 </sst>
 </file>
@@ -433,7 +439,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
@@ -538,7 +544,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
@@ -547,31 +553,45 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C16" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
